--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/5.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/5.xlsx
@@ -426,13 +426,13 @@
         <v>-8.691786611083387</v>
       </c>
       <c r="E2">
-        <v>-17.619728381302</v>
+        <v>-17.85548979508934</v>
       </c>
       <c r="F2">
-        <v>-3.788503672520129</v>
+        <v>-3.310607749068858</v>
       </c>
       <c r="G2">
-        <v>-9.55087206273708</v>
+        <v>-11.40958778739751</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.116562219725898</v>
       </c>
       <c r="E3">
-        <v>-18.00246594748229</v>
+        <v>-17.99697743698499</v>
       </c>
       <c r="F3">
-        <v>-3.525912034200088</v>
+        <v>-3.358774000072038</v>
       </c>
       <c r="G3">
-        <v>-9.555106250481808</v>
+        <v>-10.72369903093468</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.503722449880776</v>
       </c>
       <c r="E4">
-        <v>-18.75661083787566</v>
+        <v>-18.49712927723615</v>
       </c>
       <c r="F4">
-        <v>-3.022265481665392</v>
+        <v>-3.019533525970959</v>
       </c>
       <c r="G4">
-        <v>-9.143171758484755</v>
+        <v>-10.37650556750362</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.796185594355146</v>
       </c>
       <c r="E5">
-        <v>-18.96050538007102</v>
+        <v>-19.60283771874101</v>
       </c>
       <c r="F5">
-        <v>-3.389589267456179</v>
+        <v>-3.102516058913802</v>
       </c>
       <c r="G5">
-        <v>-9.298906441743149</v>
+        <v>-11.3425856562282</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.998581094870822</v>
       </c>
       <c r="E6">
-        <v>-20.10305748610228</v>
+        <v>-18.89919889895518</v>
       </c>
       <c r="F6">
-        <v>-3.252530910458585</v>
+        <v>-2.790547096447689</v>
       </c>
       <c r="G6">
-        <v>-9.40292709313259</v>
+        <v>-11.11796845193419</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.08623303824945</v>
       </c>
       <c r="E7">
-        <v>-19.95044338356978</v>
+        <v>-20.6491144673692</v>
       </c>
       <c r="F7">
-        <v>-3.00492526682259</v>
+        <v>-2.924552919565968</v>
       </c>
       <c r="G7">
-        <v>-9.399460951952973</v>
+        <v>-11.19537231718789</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.0577249375966</v>
       </c>
       <c r="E8">
-        <v>-20.63492222982916</v>
+        <v>-20.7875046330436</v>
       </c>
       <c r="F8">
-        <v>-3.026991317698363</v>
+        <v>-2.836576159551647</v>
       </c>
       <c r="G8">
-        <v>-9.271326286855482</v>
+        <v>-10.94422109039662</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.902481772120582</v>
       </c>
       <c r="E9">
-        <v>-20.80224934441258</v>
+        <v>-21.27708701496086</v>
       </c>
       <c r="F9">
-        <v>-2.938351035394399</v>
+        <v>-2.343690927946718</v>
       </c>
       <c r="G9">
-        <v>-9.016599670881799</v>
+        <v>-10.82576646045595</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.609121131575007</v>
       </c>
       <c r="E10">
-        <v>-21.99830989931847</v>
+        <v>-21.7548500797181</v>
       </c>
       <c r="F10">
-        <v>-2.881612010139647</v>
+        <v>-2.919938084764972</v>
       </c>
       <c r="G10">
-        <v>-8.744939614474745</v>
+        <v>-10.07260079754406</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.177878793358873</v>
       </c>
       <c r="E11">
-        <v>-22.62547637853677</v>
+        <v>-22.34989156432598</v>
       </c>
       <c r="F11">
-        <v>-2.766536038910143</v>
+        <v>-2.745739875262861</v>
       </c>
       <c r="G11">
-        <v>-7.930691075817761</v>
+        <v>-10.55109380760816</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.60954978470666</v>
       </c>
       <c r="E12">
-        <v>-23.43660305736866</v>
+        <v>-23.72133538907494</v>
       </c>
       <c r="F12">
-        <v>-2.793781871155621</v>
+        <v>-2.340533191407247</v>
       </c>
       <c r="G12">
-        <v>-7.258832411350371</v>
+        <v>-9.315253915616072</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.905638380815109</v>
       </c>
       <c r="E13">
-        <v>-23.26644111805644</v>
+        <v>-24.3630609122279</v>
       </c>
       <c r="F13">
-        <v>-2.681918308714173</v>
+        <v>-2.422861314101878</v>
       </c>
       <c r="G13">
-        <v>-7.812041123690282</v>
+        <v>-9.24244508757088</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.089422169088582</v>
       </c>
       <c r="E14">
-        <v>-25.1277299762151</v>
+        <v>-25.30706660386686</v>
       </c>
       <c r="F14">
-        <v>-2.809732913863928</v>
+        <v>-2.040631056897714</v>
       </c>
       <c r="G14">
-        <v>-7.125950423949564</v>
+        <v>-8.599874819489422</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.180713438049565</v>
       </c>
       <c r="E15">
-        <v>-25.61543304141918</v>
+        <v>-26.37612610522764</v>
       </c>
       <c r="F15">
-        <v>-2.264040088697934</v>
+        <v>-1.97395245117677</v>
       </c>
       <c r="G15">
-        <v>-6.33464065533419</v>
+        <v>-7.915237449240443</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.208823782695848</v>
       </c>
       <c r="E16">
-        <v>-26.38910018325962</v>
+        <v>-27.331579779158</v>
       </c>
       <c r="F16">
-        <v>-2.167401919119941</v>
+        <v>-1.768347519964919</v>
       </c>
       <c r="G16">
-        <v>-5.976969315271331</v>
+        <v>-8.115853198374738</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.215880309736665</v>
       </c>
       <c r="E17">
-        <v>-26.53008063606642</v>
+        <v>-28.03981500006161</v>
       </c>
       <c r="F17">
-        <v>-2.232744368220169</v>
+        <v>-1.497191391067334</v>
       </c>
       <c r="G17">
-        <v>-5.917452327566314</v>
+        <v>-7.647996971128316</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.236114723081131</v>
       </c>
       <c r="E18">
-        <v>-27.93172938244653</v>
+        <v>-27.6794390385312</v>
       </c>
       <c r="F18">
-        <v>-1.865840564702601</v>
+        <v>-1.302852256533556</v>
       </c>
       <c r="G18">
-        <v>-5.088011695429614</v>
+        <v>-7.324490461030735</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.311729434226851</v>
       </c>
       <c r="E19">
-        <v>-29.04036774663435</v>
+        <v>-28.81312892092945</v>
       </c>
       <c r="F19">
-        <v>-1.682795391338591</v>
+        <v>-1.312258368392345</v>
       </c>
       <c r="G19">
-        <v>-4.836982958823298</v>
+        <v>-6.587860973087504</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.4794042743342</v>
       </c>
       <c r="E20">
-        <v>-29.61110943971708</v>
+        <v>-29.42856665246789</v>
       </c>
       <c r="F20">
-        <v>-1.352204729657545</v>
+        <v>-0.9199195437718175</v>
       </c>
       <c r="G20">
-        <v>-3.841157618428368</v>
+        <v>-6.529754277782216</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7616943224341582</v>
       </c>
       <c r="E21">
-        <v>-29.87026495022804</v>
+        <v>-30.42106550801799</v>
       </c>
       <c r="F21">
-        <v>-1.250470443817529</v>
+        <v>-0.6367554010032513</v>
       </c>
       <c r="G21">
-        <v>-4.370315217425474</v>
+        <v>-5.696019868081081</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.1871332471223088</v>
       </c>
       <c r="E22">
-        <v>-29.25731787939382</v>
+        <v>-31.1565734636328</v>
       </c>
       <c r="F22">
-        <v>-1.059866417902974</v>
+        <v>-0.7426489195727233</v>
       </c>
       <c r="G22">
-        <v>-4.215113531998901</v>
+        <v>-5.884833522367875</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.2339832815487158</v>
       </c>
       <c r="E23">
-        <v>-30.64055611469576</v>
+        <v>-30.88170414831522</v>
       </c>
       <c r="F23">
-        <v>-0.8105352849669484</v>
+        <v>-0.8325309246134837</v>
       </c>
       <c r="G23">
-        <v>-3.649477031704566</v>
+        <v>-5.605102355936077</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.4996493063370052</v>
       </c>
       <c r="E24">
-        <v>-31.10068077319313</v>
+        <v>-31.71796159365268</v>
       </c>
       <c r="F24">
-        <v>-0.9422382467054446</v>
+        <v>-0.5248462783546494</v>
       </c>
       <c r="G24">
-        <v>-4.108858262370454</v>
+        <v>-5.251138826877201</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6064140613785108</v>
       </c>
       <c r="E25">
-        <v>-31.68197607495073</v>
+        <v>-31.03052338962929</v>
       </c>
       <c r="F25">
-        <v>-0.735089238654775</v>
+        <v>-0.368255017999042</v>
       </c>
       <c r="G25">
-        <v>-3.262192861792926</v>
+        <v>-5.900187832579014</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5690032137308387</v>
       </c>
       <c r="E26">
-        <v>-31.14814144503051</v>
+        <v>-31.24154122143872</v>
       </c>
       <c r="F26">
-        <v>-0.335028373105351</v>
+        <v>-0.2953031859366979</v>
       </c>
       <c r="G26">
-        <v>-3.41970530800591</v>
+        <v>-5.903968475584862</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3996676193738347</v>
       </c>
       <c r="E27">
-        <v>-31.52234057346934</v>
+        <v>-31.40424929253431</v>
       </c>
       <c r="F27">
-        <v>-0.5400575889722566</v>
+        <v>-0.4412143053680112</v>
       </c>
       <c r="G27">
-        <v>-3.665162396469633</v>
+        <v>-6.302303246506589</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1163096508320091</v>
       </c>
       <c r="E28">
-        <v>-31.87329051635277</v>
+        <v>-32.83155637264189</v>
       </c>
       <c r="F28">
-        <v>-0.5910353189405382</v>
+        <v>-0.4116382756184577</v>
       </c>
       <c r="G28">
-        <v>-4.349164141975071</v>
+        <v>-6.163866163690886</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2558340166045169</v>
       </c>
       <c r="E29">
-        <v>-31.07635154658692</v>
+        <v>-31.5712594139372</v>
       </c>
       <c r="F29">
-        <v>-0.5198760739378523</v>
+        <v>-0.4221444593881638</v>
       </c>
       <c r="G29">
-        <v>-3.919395741157964</v>
+        <v>-5.607764034549651</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.6968941693870118</v>
       </c>
       <c r="E30">
-        <v>-31.1322532939746</v>
+        <v>-31.65964843385591</v>
       </c>
       <c r="F30">
-        <v>-0.4240803540085062</v>
+        <v>-0.3946426616152202</v>
       </c>
       <c r="G30">
-        <v>-4.112205223910657</v>
+        <v>-5.665178825837232</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.18019617202198</v>
       </c>
       <c r="E31">
-        <v>-31.38855360162373</v>
+        <v>-31.45126164544494</v>
       </c>
       <c r="F31">
-        <v>-0.5564335841582001</v>
+        <v>-0.5941955405822184</v>
       </c>
       <c r="G31">
-        <v>-4.245299086225976</v>
+        <v>-6.440611218046261</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.683304356748417</v>
       </c>
       <c r="E32">
-        <v>-30.7114833388409</v>
+        <v>-30.54110856125032</v>
       </c>
       <c r="F32">
-        <v>-0.908716703016357</v>
+        <v>-0.808462709725144</v>
       </c>
       <c r="G32">
-        <v>-4.371384523634659</v>
+        <v>-6.347919253492207</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.187682761844304</v>
       </c>
       <c r="E33">
-        <v>-29.87459417137937</v>
+        <v>-30.73670920330063</v>
       </c>
       <c r="F33">
-        <v>-0.930928546555023</v>
+        <v>-0.8228671904924246</v>
       </c>
       <c r="G33">
-        <v>-4.115707781091205</v>
+        <v>-5.627623997239739</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.671210633966901</v>
       </c>
       <c r="E34">
-        <v>-29.65583038477983</v>
+        <v>-30.07778906434055</v>
       </c>
       <c r="F34">
-        <v>-0.786090162910335</v>
+        <v>-0.7721147764577045</v>
       </c>
       <c r="G34">
-        <v>-4.363465698704722</v>
+        <v>-6.649159034292649</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.122837645211055</v>
       </c>
       <c r="E35">
-        <v>-29.18308713346009</v>
+        <v>-29.10752954464211</v>
       </c>
       <c r="F35">
-        <v>-0.6962048443999634</v>
+        <v>-0.5263232574338408</v>
       </c>
       <c r="G35">
-        <v>-4.24441848111253</v>
+        <v>-6.808018872540116</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.531204018031034</v>
       </c>
       <c r="E36">
-        <v>-28.6763644774238</v>
+        <v>-29.51539561309096</v>
       </c>
       <c r="F36">
-        <v>-0.8021770578727014</v>
+        <v>-0.3279980189577916</v>
       </c>
       <c r="G36">
-        <v>-4.807780636621387</v>
+        <v>-6.494708842703491</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.886784171403393</v>
       </c>
       <c r="E37">
-        <v>-28.81402103030897</v>
+        <v>-29.33302037938005</v>
       </c>
       <c r="F37">
-        <v>-1.108376441378316</v>
+        <v>-0.5855407579577691</v>
       </c>
       <c r="G37">
-        <v>-4.928297736433015</v>
+        <v>-6.518104468029521</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.187836581781931</v>
       </c>
       <c r="E38">
-        <v>-27.86281959347182</v>
+        <v>-28.30880635611723</v>
       </c>
       <c r="F38">
-        <v>-0.8907353318037882</v>
+        <v>-0.7008279628749875</v>
       </c>
       <c r="G38">
-        <v>-5.821688176751816</v>
+        <v>-6.800523797439206</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.430612939988062</v>
       </c>
       <c r="E39">
-        <v>-27.3053101014395</v>
+        <v>-27.64432072260172</v>
       </c>
       <c r="F39">
-        <v>-0.8090872987468549</v>
+        <v>-0.4221535714295946</v>
       </c>
       <c r="G39">
-        <v>-5.163790082823532</v>
+        <v>-6.928446587622184</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.614964019046937</v>
       </c>
       <c r="E40">
-        <v>-26.63620089596216</v>
+        <v>-27.59608341747202</v>
       </c>
       <c r="F40">
-        <v>-0.8907295332319686</v>
+        <v>-0.2474732520990545</v>
       </c>
       <c r="G40">
-        <v>-5.419062938811193</v>
+        <v>-6.931949144802733</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.746056376601477</v>
       </c>
       <c r="E41">
-        <v>-26.62649637616372</v>
+        <v>-26.7368824585747</v>
       </c>
       <c r="F41">
-        <v>-0.6772882463896339</v>
+        <v>-0.3461127573222112</v>
       </c>
       <c r="G41">
-        <v>-5.64179313214782</v>
+        <v>-7.203254972837086</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.825150278687848</v>
       </c>
       <c r="E42">
-        <v>-24.99004172401188</v>
+        <v>-25.99852835704607</v>
       </c>
       <c r="F42">
-        <v>-0.8677092031081702</v>
+        <v>-0.7810586593057308</v>
       </c>
       <c r="G42">
-        <v>-5.980600983727911</v>
+        <v>-6.185745559159929</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.860332474568129</v>
       </c>
       <c r="E43">
-        <v>-24.97494379167031</v>
+        <v>-26.08195643368938</v>
       </c>
       <c r="F43">
-        <v>-0.6290383302787711</v>
+        <v>-0.272430305210598</v>
       </c>
       <c r="G43">
-        <v>-5.377552008294272</v>
+        <v>-6.793141280886632</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.864428790702171</v>
       </c>
       <c r="E44">
-        <v>-24.41467645896733</v>
+        <v>-24.82700760278774</v>
       </c>
       <c r="F44">
-        <v>-0.3564996561859142</v>
+        <v>-0.2405621828574982</v>
       </c>
       <c r="G44">
-        <v>-5.97556564396268</v>
+        <v>-6.818738418996277</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.844379010850327</v>
       </c>
       <c r="E45">
-        <v>-23.91559333858198</v>
+        <v>-23.49322256788657</v>
       </c>
       <c r="F45">
-        <v>-0.6447814527689757</v>
+        <v>-0.5806683008945024</v>
       </c>
       <c r="G45">
-        <v>-5.433950462101296</v>
+        <v>-6.855326568296301</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.815762649968</v>
       </c>
       <c r="E46">
-        <v>-22.91674782671013</v>
+        <v>-25.03841488336182</v>
       </c>
       <c r="F46">
-        <v>-0.7479670382986962</v>
+        <v>-0.3454782278916668</v>
       </c>
       <c r="G46">
-        <v>-5.212660356074252</v>
+        <v>-7.085667705827713</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.792173580027037</v>
       </c>
       <c r="E47">
-        <v>-22.57505182046136</v>
+        <v>-23.68851300946735</v>
       </c>
       <c r="F47">
-        <v>-0.5112759635619878</v>
+        <v>0.04273118522590474</v>
       </c>
       <c r="G47">
-        <v>-5.511639034271373</v>
+        <v>-6.623194425628145</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.780726894925611</v>
       </c>
       <c r="E48">
-        <v>-21.81376552655789</v>
+        <v>-23.34152774557762</v>
       </c>
       <c r="F48">
-        <v>-0.53707298121997</v>
+        <v>-0.08439836008173539</v>
       </c>
       <c r="G48">
-        <v>-5.454002436432662</v>
+        <v>-6.469115015139385</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.796934786863561</v>
       </c>
       <c r="E49">
-        <v>-21.64653803840264</v>
+        <v>-22.28374867296995</v>
       </c>
       <c r="F49">
-        <v>-0.4568190905019483</v>
+        <v>-0.2531815318717459</v>
       </c>
       <c r="G49">
-        <v>-5.623936049508991</v>
+        <v>-7.412315923642061</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.847355263330445</v>
       </c>
       <c r="E50">
-        <v>-20.96962627221008</v>
+        <v>-21.37115247704819</v>
       </c>
       <c r="F50">
-        <v>-0.6809214658183126</v>
+        <v>-0.3076947339151757</v>
       </c>
       <c r="G50">
-        <v>-5.763233874164905</v>
+        <v>-7.377674375119128</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.935835940158032</v>
       </c>
       <c r="E51">
-        <v>-20.47021710169618</v>
+        <v>-20.92576347297179</v>
       </c>
       <c r="F51">
-        <v>-0.5176676464419888</v>
+        <v>-0.168817282101033</v>
       </c>
       <c r="G51">
-        <v>-6.171520144977681</v>
+        <v>-7.489855521262871</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.073152374695008</v>
       </c>
       <c r="E52">
-        <v>-19.20056431569163</v>
+        <v>-20.89889603668428</v>
       </c>
       <c r="F52">
-        <v>-0.4175279678523622</v>
+        <v>-0.191582475064769</v>
       </c>
       <c r="G52">
-        <v>-5.741536558700521</v>
+        <v>-7.564303069350001</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.254033148812782</v>
       </c>
       <c r="E53">
-        <v>-19.46067533421821</v>
+        <v>-19.71182903115762</v>
       </c>
       <c r="F53">
-        <v>-0.6578779414072359</v>
+        <v>-0.01187810743624986</v>
       </c>
       <c r="G53">
-        <v>-6.049063065480039</v>
+        <v>-7.849890590840769</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.478059726192644</v>
       </c>
       <c r="E54">
-        <v>-19.02031746476433</v>
+        <v>-19.74533973881438</v>
       </c>
       <c r="F54">
-        <v>-0.7765473704300847</v>
+        <v>0.02643637004543567</v>
       </c>
       <c r="G54">
-        <v>-5.763382848714172</v>
+        <v>-7.693156122829515</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.74447797184679</v>
       </c>
       <c r="E55">
-        <v>-18.61810746035107</v>
+        <v>-20.11287521775091</v>
       </c>
       <c r="F55">
-        <v>-0.6073475298364661</v>
+        <v>-0.253275965755665</v>
       </c>
       <c r="G55">
-        <v>-6.409535127069122</v>
+        <v>-7.503561179795454</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.03659378525239</v>
       </c>
       <c r="E56">
-        <v>-18.22497704632318</v>
+        <v>-19.17645924854881</v>
       </c>
       <c r="F56">
-        <v>-0.6662022054379682</v>
+        <v>-0.177506027788997</v>
       </c>
       <c r="G56">
-        <v>-5.545313903496839</v>
+        <v>-7.694467098863066</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.348185058855882</v>
       </c>
       <c r="E57">
-        <v>-17.43027514271711</v>
+        <v>-19.01195337327216</v>
       </c>
       <c r="F57">
-        <v>-0.5856906924576758</v>
+        <v>0.07976583507026504</v>
       </c>
       <c r="G57">
-        <v>-6.602808086197313</v>
+        <v>-7.717015224531042</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.66692761524669</v>
       </c>
       <c r="E58">
-        <v>-16.98897535066963</v>
+        <v>-18.44199057771876</v>
       </c>
       <c r="F58">
-        <v>-0.7276529844798438</v>
+        <v>-0.4495634204208274</v>
       </c>
       <c r="G58">
-        <v>-6.411127499473512</v>
+        <v>-8.641918747838165</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.974475764946406</v>
       </c>
       <c r="E59">
-        <v>-16.66036210582902</v>
+        <v>-18.33068068661022</v>
       </c>
       <c r="F59">
-        <v>-0.6859223198290132</v>
+        <v>-0.2534267286229745</v>
       </c>
       <c r="G59">
-        <v>-6.556761708291591</v>
+        <v>-8.392889580737569</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.265283202838056</v>
       </c>
       <c r="E60">
-        <v>-16.43858009130337</v>
+        <v>-17.08954370143197</v>
       </c>
       <c r="F60">
-        <v>-0.5612712497905492</v>
+        <v>-0.2163258093863902</v>
       </c>
       <c r="G60">
-        <v>-6.111377464165741</v>
+        <v>-8.456303080542309</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.525374770135795</v>
       </c>
       <c r="E61">
-        <v>-15.51516537097728</v>
+        <v>-17.52042800326181</v>
       </c>
       <c r="F61">
-        <v>-1.004616797238456</v>
+        <v>-0.3300954452216799</v>
       </c>
       <c r="G61">
-        <v>-6.569146459154004</v>
+        <v>-7.766593954527167</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.745011321542768</v>
       </c>
       <c r="E62">
-        <v>-15.73407633298208</v>
+        <v>-16.96618354098903</v>
       </c>
       <c r="F62">
-        <v>-0.965167456414935</v>
+        <v>-0.6289057914943232</v>
       </c>
       <c r="G62">
-        <v>-6.904640454649285</v>
+        <v>-8.280609118227646</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.925291829369422</v>
       </c>
       <c r="E63">
-        <v>-15.79041960658551</v>
+        <v>-17.36247030140026</v>
       </c>
       <c r="F63">
-        <v>-0.6896276072217353</v>
+        <v>-0.4197123726935444</v>
       </c>
       <c r="G63">
-        <v>-6.881105786410607</v>
+        <v>-8.304984665033301</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.055838737321832</v>
       </c>
       <c r="E64">
-        <v>-15.97684329605928</v>
+        <v>-16.72391018157866</v>
       </c>
       <c r="F64">
-        <v>-1.087330939142792</v>
+        <v>-0.7261271317238872</v>
       </c>
       <c r="G64">
-        <v>-7.377369804929514</v>
+        <v>-8.366779308069336</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.136935393966228</v>
       </c>
       <c r="E65">
-        <v>-15.57414874492719</v>
+        <v>-16.99059201589037</v>
       </c>
       <c r="F65">
-        <v>-1.37964191477307</v>
+        <v>-1.015685442474663</v>
       </c>
       <c r="G65">
-        <v>-7.560353588521651</v>
+        <v>-9.410412236596882</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.171107906681742</v>
       </c>
       <c r="E66">
-        <v>-14.66400698191758</v>
+        <v>-16.17137295400677</v>
       </c>
       <c r="F66">
-        <v>-0.9761159883777359</v>
+        <v>-0.8571367499462402</v>
       </c>
       <c r="G66">
-        <v>-7.398805587296295</v>
+        <v>-9.212180080250862</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.151484956502202</v>
       </c>
       <c r="E67">
-        <v>-14.57606854516263</v>
+        <v>-16.17520857149127</v>
       </c>
       <c r="F67">
-        <v>-1.578332463273754</v>
+        <v>-0.8024636729940701</v>
       </c>
       <c r="G67">
-        <v>-7.215103415322137</v>
+        <v>-8.336789076029079</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.081431614302685</v>
       </c>
       <c r="E68">
-        <v>-15.37502721433592</v>
+        <v>-15.48521404389055</v>
       </c>
       <c r="F68">
-        <v>-1.655881734421635</v>
+        <v>-0.8724193001604883</v>
       </c>
       <c r="G68">
-        <v>-7.217093053191239</v>
+        <v>-8.747637709089251</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.960849819415359</v>
       </c>
       <c r="E69">
-        <v>-15.55247546832648</v>
+        <v>-15.92423601351217</v>
       </c>
       <c r="F69">
-        <v>-1.52492761681527</v>
+        <v>-0.7944898083747219</v>
       </c>
       <c r="G69">
-        <v>-7.147915893602629</v>
+        <v>-8.385275325997245</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.783535761035456</v>
       </c>
       <c r="E70">
-        <v>-15.1268170255015</v>
+        <v>-15.55590352315028</v>
       </c>
       <c r="F70">
-        <v>-1.756110048323362</v>
+        <v>-1.507286704605252</v>
       </c>
       <c r="G70">
-        <v>-7.110563008283031</v>
+        <v>-8.525748394319599</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.553405604951058</v>
       </c>
       <c r="E71">
-        <v>-14.35615679040215</v>
+        <v>-16.00096194862413</v>
       </c>
       <c r="F71">
-        <v>-1.829150515697805</v>
+        <v>-1.335988609380342</v>
       </c>
       <c r="G71">
-        <v>-7.047606363762712</v>
+        <v>-7.83717147487889</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.267679080742202</v>
       </c>
       <c r="E72">
-        <v>-14.65396735504258</v>
+        <v>-15.95367109456203</v>
       </c>
       <c r="F72">
-        <v>-1.502127632420617</v>
+        <v>-1.314906658979095</v>
       </c>
       <c r="G72">
-        <v>-7.183100371594002</v>
+        <v>-7.45778957716949</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.92125153534274</v>
       </c>
       <c r="E73">
-        <v>-14.36706135581262</v>
+        <v>-15.7427121329147</v>
       </c>
       <c r="F73">
-        <v>-1.898879170195857</v>
+        <v>-1.16277532872016</v>
       </c>
       <c r="G73">
-        <v>-6.713641840306574</v>
+        <v>-8.914038970075179</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.521648893307012</v>
       </c>
       <c r="E74">
-        <v>-14.75700825261311</v>
+        <v>-16.62121344803271</v>
       </c>
       <c r="F74">
-        <v>-1.934298503604758</v>
+        <v>-1.354927573310547</v>
       </c>
       <c r="G74">
-        <v>-6.907792094002671</v>
+        <v>-8.335977992371959</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.067649494703741</v>
       </c>
       <c r="E75">
-        <v>-15.65252304457794</v>
+        <v>-15.87929543746005</v>
       </c>
       <c r="F75">
-        <v>-1.701156154821643</v>
+        <v>-1.558847605225104</v>
       </c>
       <c r="G75">
-        <v>-5.73414079996579</v>
+        <v>-7.837992490172629</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.562543568691542</v>
       </c>
       <c r="E76">
-        <v>-15.43342641513883</v>
+        <v>-16.12560366721125</v>
       </c>
       <c r="F76">
-        <v>-1.951091167594309</v>
+        <v>-1.227518868188163</v>
       </c>
       <c r="G76">
-        <v>-5.886449068591039</v>
+        <v>-7.550418641358298</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.017880957071509</v>
       </c>
       <c r="E77">
-        <v>-15.91143401749248</v>
+        <v>-17.2445352528185</v>
       </c>
       <c r="F77">
-        <v>-2.172909733981155</v>
+        <v>-1.502827602875982</v>
       </c>
       <c r="G77">
-        <v>-5.627259837230419</v>
+        <v>-7.495298058129433</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.438774816379036</v>
       </c>
       <c r="E78">
-        <v>-16.98230037998232</v>
+        <v>-17.73887253244381</v>
       </c>
       <c r="F78">
-        <v>-1.786765440798763</v>
+        <v>-1.690410572872527</v>
       </c>
       <c r="G78">
-        <v>-5.794425834235918</v>
+        <v>-7.11266189415493</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.839941824500963</v>
       </c>
       <c r="E79">
-        <v>-16.70293428997513</v>
+        <v>-17.90308858538396</v>
       </c>
       <c r="F79">
-        <v>-1.93315121475188</v>
+        <v>-1.81729823489855</v>
       </c>
       <c r="G79">
-        <v>-5.46791003824314</v>
+        <v>-6.518273305852023</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.23790580777134</v>
       </c>
       <c r="E80">
-        <v>-16.99195508656668</v>
+        <v>-18.07480831975482</v>
       </c>
       <c r="F80">
-        <v>-2.103686383598812</v>
+        <v>-1.90093683482441</v>
       </c>
       <c r="G80">
-        <v>-5.035129040985296</v>
+        <v>-6.848960389224283</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.643639198003193</v>
       </c>
       <c r="E81">
-        <v>-18.26822397309643</v>
+        <v>-17.86668871131031</v>
       </c>
       <c r="F81">
-        <v>-1.965622388574218</v>
+        <v>-1.720387532445036</v>
       </c>
       <c r="G81">
-        <v>-4.69438452026473</v>
+        <v>-6.846636386255715</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.078930634698213</v>
       </c>
       <c r="E82">
-        <v>-18.55925994062139</v>
+        <v>-19.30944694473206</v>
       </c>
       <c r="F82">
-        <v>-2.218098004171271</v>
+        <v>-2.01467085086138</v>
       </c>
       <c r="G82">
-        <v>-3.868049179843867</v>
+        <v>-6.247967262570531</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.559661211333593</v>
       </c>
       <c r="E83">
-        <v>-19.30648079425703</v>
+        <v>-20.02350578320954</v>
       </c>
       <c r="F83">
-        <v>-2.071177933243348</v>
+        <v>-2.105977647834955</v>
       </c>
       <c r="G83">
-        <v>-4.090686677905394</v>
+        <v>-6.057806216249255</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.098617081680061</v>
       </c>
       <c r="E84">
-        <v>-20.38109673322523</v>
+        <v>-19.9931967066762</v>
       </c>
       <c r="F84">
-        <v>-2.408379795166137</v>
+        <v>-1.877322565272805</v>
       </c>
       <c r="G84">
-        <v>-3.881721732921057</v>
+        <v>-5.742324468538868</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.7175800495166809</v>
       </c>
       <c r="E85">
-        <v>-20.21178161855244</v>
+        <v>-21.96186926897875</v>
       </c>
       <c r="F85">
-        <v>-2.371409757979195</v>
+        <v>-2.2044953830499</v>
       </c>
       <c r="G85">
-        <v>-3.843369062848601</v>
+        <v>-5.61403751834657</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4257506225493981</v>
       </c>
       <c r="E86">
-        <v>-22.67248193873639</v>
+        <v>-21.85501992476777</v>
       </c>
       <c r="F86">
-        <v>-2.198111155476524</v>
+        <v>-2.169858028469242</v>
       </c>
       <c r="G86">
-        <v>-3.929502836689359</v>
+        <v>-5.294785059266953</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2357172816264472</v>
       </c>
       <c r="E87">
-        <v>-22.88623949732045</v>
+        <v>-23.7520067435289</v>
       </c>
       <c r="F87">
-        <v>-2.368932111077422</v>
+        <v>-2.34739621533944</v>
       </c>
       <c r="G87">
-        <v>-3.855661118435914</v>
+        <v>-5.363743722849972</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.1571690641955425</v>
       </c>
       <c r="E88">
-        <v>-24.08977656281301</v>
+        <v>-24.65727586850625</v>
       </c>
       <c r="F88">
-        <v>-2.539884777095364</v>
+        <v>-2.367328391785602</v>
       </c>
       <c r="G88">
-        <v>-3.825028640561039</v>
+        <v>-5.607154894170425</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1897143114925208</v>
       </c>
       <c r="E89">
-        <v>-25.12605896930627</v>
+        <v>-26.08419802832318</v>
       </c>
       <c r="F89">
-        <v>-2.750694340699005</v>
+        <v>-1.987103612063615</v>
       </c>
       <c r="G89">
-        <v>-3.522126965899882</v>
+        <v>-5.317376222026939</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.3372734568550461</v>
       </c>
       <c r="E90">
-        <v>-26.99702064794532</v>
+        <v>-27.21150729084462</v>
       </c>
       <c r="F90">
-        <v>-2.684557487259492</v>
+        <v>-2.582467831803676</v>
       </c>
       <c r="G90">
-        <v>-3.509470750303248</v>
+        <v>-5.633629326847977</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5929822705743418</v>
       </c>
       <c r="E91">
-        <v>-28.85697360627172</v>
+        <v>-28.58511119769524</v>
       </c>
       <c r="F91">
-        <v>-2.492836822085964</v>
+        <v>-2.449679708767512</v>
       </c>
       <c r="G91">
-        <v>-3.040343273569746</v>
+        <v>-5.277719197012011</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.9471394478948476</v>
       </c>
       <c r="E92">
-        <v>-30.6029720446691</v>
+        <v>-31.11646476934686</v>
       </c>
       <c r="F92">
-        <v>-2.901448924334487</v>
+        <v>-2.426395129442221</v>
       </c>
       <c r="G92">
-        <v>-3.23024278679342</v>
+        <v>-5.854479130318297</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.392638216000617</v>
       </c>
       <c r="E93">
-        <v>-32.16113843817634</v>
+        <v>-32.86330097543566</v>
       </c>
       <c r="F93">
-        <v>-2.828285858584429</v>
+        <v>-2.761313182435492</v>
       </c>
       <c r="G93">
-        <v>-3.187205694782894</v>
+        <v>-5.466119033106394</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.909106296552922</v>
       </c>
       <c r="E94">
-        <v>-33.82076529182542</v>
+        <v>-33.87279292969954</v>
       </c>
       <c r="F94">
-        <v>-2.836168602789469</v>
+        <v>-2.955009503864698</v>
       </c>
       <c r="G94">
-        <v>-3.076676510863247</v>
+        <v>-6.007939468791213</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.483187691299662</v>
       </c>
       <c r="E95">
-        <v>-36.29763679269076</v>
+        <v>-35.09580469766209</v>
       </c>
       <c r="F95">
-        <v>-3.026956526267446</v>
+        <v>-2.892224224936911</v>
       </c>
       <c r="G95">
-        <v>-3.745112071243032</v>
+        <v>-6.190271074912113</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.102700370667817</v>
       </c>
       <c r="E96">
-        <v>-36.80621612307019</v>
+        <v>-37.28842162082896</v>
       </c>
       <c r="F96">
-        <v>-3.504591513986835</v>
+        <v>-3.36822567213798</v>
       </c>
       <c r="G96">
-        <v>-3.759536118157636</v>
+        <v>-5.996624024137984</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.739483006895059</v>
       </c>
       <c r="E97">
-        <v>-39.06123994653677</v>
+        <v>-39.04905608721914</v>
       </c>
       <c r="F97">
-        <v>-3.231628715783744</v>
+        <v>-3.291556955539275</v>
       </c>
       <c r="G97">
-        <v>-4.627769722923516</v>
+        <v>-6.677652899749156</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.392937889181172</v>
       </c>
       <c r="E98">
-        <v>-41.09075708560638</v>
+        <v>-40.75943128483517</v>
       </c>
       <c r="F98">
-        <v>-3.379539514125416</v>
+        <v>-3.416991661140787</v>
       </c>
       <c r="G98">
-        <v>-4.428865525833024</v>
+        <v>-6.780101042007442</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.028553359689397</v>
       </c>
       <c r="E99">
-        <v>-43.46323141093589</v>
+        <v>-43.50280574528892</v>
       </c>
       <c r="F99">
-        <v>-3.572298123654653</v>
+        <v>-3.403354248588499</v>
       </c>
       <c r="G99">
-        <v>-4.926198850561117</v>
+        <v>-6.970480584334311</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.661015810360555</v>
       </c>
       <c r="E100">
-        <v>-45.27001102746422</v>
+        <v>-46.68405194296633</v>
       </c>
       <c r="F100">
-        <v>-3.534053229034802</v>
+        <v>-3.795419711966102</v>
       </c>
       <c r="G100">
-        <v>-5.41907949153889</v>
+        <v>-7.684095159688529</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.240247347530567</v>
       </c>
       <c r="E101">
-        <v>-47.26004893013496</v>
+        <v>-46.72357193563128</v>
       </c>
       <c r="F101">
-        <v>-3.856444710162939</v>
+        <v>-3.797520451699602</v>
       </c>
       <c r="G101">
-        <v>-6.034049741459445</v>
+        <v>-8.157377371073817</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.831704648969484</v>
       </c>
       <c r="E102">
-        <v>-50.03135275403101</v>
+        <v>-49.56172056435455</v>
       </c>
       <c r="F102">
-        <v>-3.892279055640643</v>
+        <v>-4.266086473093142</v>
       </c>
       <c r="G102">
-        <v>-5.896794523401262</v>
+        <v>-8.115985620196309</v>
       </c>
     </row>
   </sheetData>
